--- a/planilha.xlsx
+++ b/planilha.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Natalia Bastos\sistema_leads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6DECFC1-0399-4FC2-898C-98AC7E152AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5BD12F0-D42A-450A-9E02-A31AE01A2F4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="desistencias_historico" sheetId="45" r:id="rId1"/>
@@ -26,13 +26,14 @@
     <sheet name="30 e 31 Outubro" sheetId="11" state="hidden" r:id="rId11"/>
     <sheet name="Desistência" sheetId="12" state="hidden" r:id="rId12"/>
     <sheet name="novembro" sheetId="44" r:id="rId13"/>
-    <sheet name="11 e 12 de dezembro" sheetId="15" state="hidden" r:id="rId14"/>
-    <sheet name="Desistências--" sheetId="16" state="hidden" r:id="rId15"/>
-    <sheet name="22 a 23 janeiro-2026 " sheetId="17" state="hidden" r:id="rId16"/>
-    <sheet name=" Desistências- Janeiro1" sheetId="18" state="hidden" r:id="rId17"/>
+    <sheet name="municipios_ba" sheetId="47" r:id="rId14"/>
+    <sheet name="11 e 12 de dezembro" sheetId="15" state="hidden" r:id="rId15"/>
+    <sheet name="Desistências--" sheetId="16" state="hidden" r:id="rId16"/>
+    <sheet name="22 a 23 janeiro-2026 " sheetId="17" state="hidden" r:id="rId17"/>
+    <sheet name=" Desistências- Janeiro1" sheetId="18" state="hidden" r:id="rId18"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="15" hidden="1">'22 a 23 janeiro-2026 '!$A$5:$J$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="16" hidden="1">'22 a 23 janeiro-2026 '!$A$5:$J$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">Desistência!$A$2:$E$58</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">Desistências!$A$1:$E$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Desistências- Histórico'!$A$1:$E$53</definedName>
@@ -58,7 +59,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3361" uniqueCount="890">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4197" uniqueCount="1310">
   <si>
     <t xml:space="preserve">ENCERRADO </t>
   </si>
@@ -1894,9 +1895,6 @@
     <t xml:space="preserve">DEMONSTRARAM INTERESSE, MAS NÃO ATENDEM. </t>
   </si>
   <si>
-    <t xml:space="preserve">ILHÈUS </t>
-  </si>
-  <si>
     <t xml:space="preserve">ITABELA </t>
   </si>
   <si>
@@ -2729,6 +2727,1269 @@
   </si>
   <si>
     <t>MOTIVO_OBJECAO</t>
+  </si>
+  <si>
+    <t>UF</t>
+  </si>
+  <si>
+    <t>Nome_Município</t>
+  </si>
+  <si>
+    <t>BA</t>
+  </si>
+  <si>
+    <t>Abaíra</t>
+  </si>
+  <si>
+    <t>Abaré</t>
+  </si>
+  <si>
+    <t>Acajutiba</t>
+  </si>
+  <si>
+    <t>Adustina</t>
+  </si>
+  <si>
+    <t>Água Fria</t>
+  </si>
+  <si>
+    <t>Aiquara</t>
+  </si>
+  <si>
+    <t>Alagoinhas</t>
+  </si>
+  <si>
+    <t>Alcobaça</t>
+  </si>
+  <si>
+    <t>Almadina</t>
+  </si>
+  <si>
+    <t>Amargosa</t>
+  </si>
+  <si>
+    <t>Amélia Rodrigues</t>
+  </si>
+  <si>
+    <t>América Dourada</t>
+  </si>
+  <si>
+    <t>Anagé</t>
+  </si>
+  <si>
+    <t>Andaraí</t>
+  </si>
+  <si>
+    <t>Andorinha</t>
+  </si>
+  <si>
+    <t>Angical</t>
+  </si>
+  <si>
+    <t>Anguera</t>
+  </si>
+  <si>
+    <t>Antas</t>
+  </si>
+  <si>
+    <t>Antônio Cardoso</t>
+  </si>
+  <si>
+    <t>Antônio Gonçalves</t>
+  </si>
+  <si>
+    <t>Aporá</t>
+  </si>
+  <si>
+    <t>Apuarema</t>
+  </si>
+  <si>
+    <t>Araçás</t>
+  </si>
+  <si>
+    <t>Aracatu</t>
+  </si>
+  <si>
+    <t>Araci</t>
+  </si>
+  <si>
+    <t>Aramari</t>
+  </si>
+  <si>
+    <t>Arataca</t>
+  </si>
+  <si>
+    <t>Aratuípe</t>
+  </si>
+  <si>
+    <t>Aurelino Leal</t>
+  </si>
+  <si>
+    <t>Baianópolis</t>
+  </si>
+  <si>
+    <t>Baixa Grande</t>
+  </si>
+  <si>
+    <t>Banzaê</t>
+  </si>
+  <si>
+    <t>Barra</t>
+  </si>
+  <si>
+    <t>Barra da Estiva</t>
+  </si>
+  <si>
+    <t>Barra do Choça</t>
+  </si>
+  <si>
+    <t>Barra do Mendes</t>
+  </si>
+  <si>
+    <t>Barra do Rocha</t>
+  </si>
+  <si>
+    <t>Barreiras</t>
+  </si>
+  <si>
+    <t>Barro Alto</t>
+  </si>
+  <si>
+    <t>Barro Preto</t>
+  </si>
+  <si>
+    <t>Barrocas</t>
+  </si>
+  <si>
+    <t>Belmonte</t>
+  </si>
+  <si>
+    <t>Belo Campo</t>
+  </si>
+  <si>
+    <t>Biritinga</t>
+  </si>
+  <si>
+    <t>Boa Nova</t>
+  </si>
+  <si>
+    <t>Boa Vista do Tupim</t>
+  </si>
+  <si>
+    <t>Bom Jesus da Lapa</t>
+  </si>
+  <si>
+    <t>Bom Jesus da Serra</t>
+  </si>
+  <si>
+    <t>Boninal</t>
+  </si>
+  <si>
+    <t>Bonito</t>
+  </si>
+  <si>
+    <t>Boquira</t>
+  </si>
+  <si>
+    <t>Botuporã</t>
+  </si>
+  <si>
+    <t>Brejões</t>
+  </si>
+  <si>
+    <t>Brejolândia</t>
+  </si>
+  <si>
+    <t>Brotas de Macaúbas</t>
+  </si>
+  <si>
+    <t>Brumado</t>
+  </si>
+  <si>
+    <t>Buerarema</t>
+  </si>
+  <si>
+    <t>Buritirama</t>
+  </si>
+  <si>
+    <t>Caatiba</t>
+  </si>
+  <si>
+    <t>Cabaceiras do Paraguaçu</t>
+  </si>
+  <si>
+    <t>Cachoeira</t>
+  </si>
+  <si>
+    <t>Caculé</t>
+  </si>
+  <si>
+    <t>Caém</t>
+  </si>
+  <si>
+    <t>Caetanos</t>
+  </si>
+  <si>
+    <t>Caetité</t>
+  </si>
+  <si>
+    <t>Cafarnaum</t>
+  </si>
+  <si>
+    <t>Cairu</t>
+  </si>
+  <si>
+    <t>Caldeirão Grande</t>
+  </si>
+  <si>
+    <t>Camacan</t>
+  </si>
+  <si>
+    <t>Camaçari</t>
+  </si>
+  <si>
+    <t>Camamu</t>
+  </si>
+  <si>
+    <t>Campo Alegre de Lourdes</t>
+  </si>
+  <si>
+    <t>Campo Formoso</t>
+  </si>
+  <si>
+    <t>Canápolis</t>
+  </si>
+  <si>
+    <t>Canarana</t>
+  </si>
+  <si>
+    <t>Canavieiras</t>
+  </si>
+  <si>
+    <t>Candeal</t>
+  </si>
+  <si>
+    <t>Candeias</t>
+  </si>
+  <si>
+    <t>Candiba</t>
+  </si>
+  <si>
+    <t>Cândido Sales</t>
+  </si>
+  <si>
+    <t>Cansanção</t>
+  </si>
+  <si>
+    <t>Canudos</t>
+  </si>
+  <si>
+    <t>Capela do Alto Alegre</t>
+  </si>
+  <si>
+    <t>Capim Grosso</t>
+  </si>
+  <si>
+    <t>Caraíbas</t>
+  </si>
+  <si>
+    <t>Caravelas</t>
+  </si>
+  <si>
+    <t>Cardeal da Silva</t>
+  </si>
+  <si>
+    <t>Carinhanha</t>
+  </si>
+  <si>
+    <t>Casa Nova</t>
+  </si>
+  <si>
+    <t>Castro Alves</t>
+  </si>
+  <si>
+    <t>Catolândia</t>
+  </si>
+  <si>
+    <t>Catu</t>
+  </si>
+  <si>
+    <t>Caturama</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Chorrochó</t>
+  </si>
+  <si>
+    <t>Cícero Dantas</t>
+  </si>
+  <si>
+    <t>Cipó</t>
+  </si>
+  <si>
+    <t>Coaraci</t>
+  </si>
+  <si>
+    <t>Cocos</t>
+  </si>
+  <si>
+    <t>Conceição da Feira</t>
+  </si>
+  <si>
+    <t>Conceição do Almeida</t>
+  </si>
+  <si>
+    <t>Conceição do Coité</t>
+  </si>
+  <si>
+    <t>Conceição do Jacuípe</t>
+  </si>
+  <si>
+    <t>Conde</t>
+  </si>
+  <si>
+    <t>Condeúba</t>
+  </si>
+  <si>
+    <t>Contendas do Sincorá</t>
+  </si>
+  <si>
+    <t>Coração de Maria</t>
+  </si>
+  <si>
+    <t>Cordeiros</t>
+  </si>
+  <si>
+    <t>Coribe</t>
+  </si>
+  <si>
+    <t>Coronel João Sá</t>
+  </si>
+  <si>
+    <t>Correntina</t>
+  </si>
+  <si>
+    <t>Cotegipe</t>
+  </si>
+  <si>
+    <t>Cravolândia</t>
+  </si>
+  <si>
+    <t>Crisópolis</t>
+  </si>
+  <si>
+    <t>Cristópolis</t>
+  </si>
+  <si>
+    <t>Cruz das Almas</t>
+  </si>
+  <si>
+    <t>Curaçá</t>
+  </si>
+  <si>
+    <t>Dário Meira</t>
+  </si>
+  <si>
+    <t>Dias d'Ávila</t>
+  </si>
+  <si>
+    <t>Dom Basílio</t>
+  </si>
+  <si>
+    <t>Dom Macedo Costa</t>
+  </si>
+  <si>
+    <t>Elísio Medrado</t>
+  </si>
+  <si>
+    <t>Encruzilhada</t>
+  </si>
+  <si>
+    <t>Entre Rios</t>
+  </si>
+  <si>
+    <t>Érico Cardoso</t>
+  </si>
+  <si>
+    <t>Esplanada</t>
+  </si>
+  <si>
+    <t>Euclides da Cunha</t>
+  </si>
+  <si>
+    <t>Eunápolis</t>
+  </si>
+  <si>
+    <t>Fátima</t>
+  </si>
+  <si>
+    <t>Feira da Mata</t>
+  </si>
+  <si>
+    <t>Feira de Santana</t>
+  </si>
+  <si>
+    <t>Filadélfia</t>
+  </si>
+  <si>
+    <t>Firmino Alves</t>
+  </si>
+  <si>
+    <t>Floresta Azul</t>
+  </si>
+  <si>
+    <t>Formosa do Rio Preto</t>
+  </si>
+  <si>
+    <t>Gandu</t>
+  </si>
+  <si>
+    <t>Gavião</t>
+  </si>
+  <si>
+    <t>Gentio do Ouro</t>
+  </si>
+  <si>
+    <t>Glória</t>
+  </si>
+  <si>
+    <t>Gongogi</t>
+  </si>
+  <si>
+    <t>Governador Mangabeira</t>
+  </si>
+  <si>
+    <t>Guajeru</t>
+  </si>
+  <si>
+    <t>Guanambi</t>
+  </si>
+  <si>
+    <t>Guaratinga</t>
+  </si>
+  <si>
+    <t>Heliópolis</t>
+  </si>
+  <si>
+    <t>Iaçu</t>
+  </si>
+  <si>
+    <t>Ibiassucê</t>
+  </si>
+  <si>
+    <t>Ibicaraí</t>
+  </si>
+  <si>
+    <t>Ibicoara</t>
+  </si>
+  <si>
+    <t>Ibicuí</t>
+  </si>
+  <si>
+    <t>Ibipeba</t>
+  </si>
+  <si>
+    <t>Ibipitanga</t>
+  </si>
+  <si>
+    <t>Ibiquera</t>
+  </si>
+  <si>
+    <t>Ibirapitanga</t>
+  </si>
+  <si>
+    <t>Ibirapuã</t>
+  </si>
+  <si>
+    <t>Ibirataia</t>
+  </si>
+  <si>
+    <t>Ibitiara</t>
+  </si>
+  <si>
+    <t>Ibititá</t>
+  </si>
+  <si>
+    <t>Ibotirama</t>
+  </si>
+  <si>
+    <t>Ichu</t>
+  </si>
+  <si>
+    <t>Igaporã</t>
+  </si>
+  <si>
+    <t>Igrapiúna</t>
+  </si>
+  <si>
+    <t>Iguaí</t>
+  </si>
+  <si>
+    <t>Ilhéus</t>
+  </si>
+  <si>
+    <t>Inhambupe</t>
+  </si>
+  <si>
+    <t>Ipecaetá</t>
+  </si>
+  <si>
+    <t>Ipiaú</t>
+  </si>
+  <si>
+    <t>Ipirá</t>
+  </si>
+  <si>
+    <t>Ipupiara</t>
+  </si>
+  <si>
+    <t>Irajuba</t>
+  </si>
+  <si>
+    <t>Iramaia</t>
+  </si>
+  <si>
+    <t>Iraquara</t>
+  </si>
+  <si>
+    <t>Irará</t>
+  </si>
+  <si>
+    <t>Irecê</t>
+  </si>
+  <si>
+    <t>Itabela</t>
+  </si>
+  <si>
+    <t>Itaberaba</t>
+  </si>
+  <si>
+    <t>Itabuna</t>
+  </si>
+  <si>
+    <t>Itacaré</t>
+  </si>
+  <si>
+    <t>Itaeté</t>
+  </si>
+  <si>
+    <t>Itagi</t>
+  </si>
+  <si>
+    <t>Itagibá</t>
+  </si>
+  <si>
+    <t>Itagimirim</t>
+  </si>
+  <si>
+    <t>Itaguaçu da Bahia</t>
+  </si>
+  <si>
+    <t>Itaju do Colônia</t>
+  </si>
+  <si>
+    <t>Itajuípe</t>
+  </si>
+  <si>
+    <t>Itamaraju</t>
+  </si>
+  <si>
+    <t>Itamari</t>
+  </si>
+  <si>
+    <t>Itambé</t>
+  </si>
+  <si>
+    <t>Itanagra</t>
+  </si>
+  <si>
+    <t>Itanhém</t>
+  </si>
+  <si>
+    <t>Itaparica</t>
+  </si>
+  <si>
+    <t>Itapé</t>
+  </si>
+  <si>
+    <t>Itapebi</t>
+  </si>
+  <si>
+    <t>Itapetinga</t>
+  </si>
+  <si>
+    <t>Itapicuru</t>
+  </si>
+  <si>
+    <t>Itapitanga</t>
+  </si>
+  <si>
+    <t>Itaquara</t>
+  </si>
+  <si>
+    <t>Itarantim</t>
+  </si>
+  <si>
+    <t>Itatim</t>
+  </si>
+  <si>
+    <t>Itiruçu</t>
+  </si>
+  <si>
+    <t>Itiúba</t>
+  </si>
+  <si>
+    <t>Itororó</t>
+  </si>
+  <si>
+    <t>Ituaçu</t>
+  </si>
+  <si>
+    <t>Ituberá</t>
+  </si>
+  <si>
+    <t>Iuiu</t>
+  </si>
+  <si>
+    <t>Jaborandi</t>
+  </si>
+  <si>
+    <t>Jacaraci</t>
+  </si>
+  <si>
+    <t>Jacobina</t>
+  </si>
+  <si>
+    <t>Jaguaquara</t>
+  </si>
+  <si>
+    <t>Jaguarari</t>
+  </si>
+  <si>
+    <t>Jaguaripe</t>
+  </si>
+  <si>
+    <t>Jandaíra</t>
+  </si>
+  <si>
+    <t>Jequié</t>
+  </si>
+  <si>
+    <t>Jeremoabo</t>
+  </si>
+  <si>
+    <t>Jiquiriçá</t>
+  </si>
+  <si>
+    <t>Jitaúna</t>
+  </si>
+  <si>
+    <t>João Dourado</t>
+  </si>
+  <si>
+    <t>Juazeiro</t>
+  </si>
+  <si>
+    <t>Jucuruçu</t>
+  </si>
+  <si>
+    <t>Jussara</t>
+  </si>
+  <si>
+    <t>Jussari</t>
+  </si>
+  <si>
+    <t>Jussiape</t>
+  </si>
+  <si>
+    <t>Lafaiete Coutinho</t>
+  </si>
+  <si>
+    <t>Lagoa Real</t>
+  </si>
+  <si>
+    <t>Laje</t>
+  </si>
+  <si>
+    <t>Lajedão</t>
+  </si>
+  <si>
+    <t>Lajedinho</t>
+  </si>
+  <si>
+    <t>Lajedo do Tabocal</t>
+  </si>
+  <si>
+    <t>Lamarão</t>
+  </si>
+  <si>
+    <t>Lapão</t>
+  </si>
+  <si>
+    <t>Lauro de Freitas</t>
+  </si>
+  <si>
+    <t>Lençóis</t>
+  </si>
+  <si>
+    <t>Licínio de Almeida</t>
+  </si>
+  <si>
+    <t>Livramento de Nossa Senhora</t>
+  </si>
+  <si>
+    <t>Luís Eduardo Magalhães</t>
+  </si>
+  <si>
+    <t>Macajuba</t>
+  </si>
+  <si>
+    <t>Macarani</t>
+  </si>
+  <si>
+    <t>Macaúbas</t>
+  </si>
+  <si>
+    <t>Macururé</t>
+  </si>
+  <si>
+    <t>Madre de Deus</t>
+  </si>
+  <si>
+    <t>Maetinga</t>
+  </si>
+  <si>
+    <t>Maiquinique</t>
+  </si>
+  <si>
+    <t>Mairi</t>
+  </si>
+  <si>
+    <t>Malhada</t>
+  </si>
+  <si>
+    <t>Malhada de Pedras</t>
+  </si>
+  <si>
+    <t>Manoel Vitorino</t>
+  </si>
+  <si>
+    <t>Mansidão</t>
+  </si>
+  <si>
+    <t>Maracás</t>
+  </si>
+  <si>
+    <t>Maragogipe</t>
+  </si>
+  <si>
+    <t>Maraú</t>
+  </si>
+  <si>
+    <t>Marcionílio Souza</t>
+  </si>
+  <si>
+    <t>Mascote</t>
+  </si>
+  <si>
+    <t>Mata de São João</t>
+  </si>
+  <si>
+    <t>Matina</t>
+  </si>
+  <si>
+    <t>Medeiros Neto</t>
+  </si>
+  <si>
+    <t>Miguel Calmon</t>
+  </si>
+  <si>
+    <t>Milagres</t>
+  </si>
+  <si>
+    <t>Mirangaba</t>
+  </si>
+  <si>
+    <t>Mirante</t>
+  </si>
+  <si>
+    <t>Monte Santo</t>
+  </si>
+  <si>
+    <t>Morpará</t>
+  </si>
+  <si>
+    <t>Morro do Chapéu</t>
+  </si>
+  <si>
+    <t>Mortugaba</t>
+  </si>
+  <si>
+    <t>Mucugê</t>
+  </si>
+  <si>
+    <t>Mucuri</t>
+  </si>
+  <si>
+    <t>Mulungu do Morro</t>
+  </si>
+  <si>
+    <t>Mundo Novo</t>
+  </si>
+  <si>
+    <t>Muniz Ferreira</t>
+  </si>
+  <si>
+    <t>Muquém do São Francisco</t>
+  </si>
+  <si>
+    <t>Muritiba</t>
+  </si>
+  <si>
+    <t>Mutuípe</t>
+  </si>
+  <si>
+    <t>Nazaré</t>
+  </si>
+  <si>
+    <t>Nilo Peçanha</t>
+  </si>
+  <si>
+    <t>Nordestina</t>
+  </si>
+  <si>
+    <t>Nova Canaã</t>
+  </si>
+  <si>
+    <t>Nova Fátima</t>
+  </si>
+  <si>
+    <t>Nova Ibiá</t>
+  </si>
+  <si>
+    <t>Nova Itarana</t>
+  </si>
+  <si>
+    <t>Nova Redenção</t>
+  </si>
+  <si>
+    <t>Nova Soure</t>
+  </si>
+  <si>
+    <t>Nova Viçosa</t>
+  </si>
+  <si>
+    <t>Novo Horizonte</t>
+  </si>
+  <si>
+    <t>Novo Triunfo</t>
+  </si>
+  <si>
+    <t>Olindina</t>
+  </si>
+  <si>
+    <t>Oliveira dos Brejinhos</t>
+  </si>
+  <si>
+    <t>Ouriçangas</t>
+  </si>
+  <si>
+    <t>Ourolândia</t>
+  </si>
+  <si>
+    <t>Palmas de Monte Alto</t>
+  </si>
+  <si>
+    <t>Palmeiras</t>
+  </si>
+  <si>
+    <t>Paramirim</t>
+  </si>
+  <si>
+    <t>Paratinga</t>
+  </si>
+  <si>
+    <t>Paripiranga</t>
+  </si>
+  <si>
+    <t>Pau Brasil</t>
+  </si>
+  <si>
+    <t>Paulo Afonso</t>
+  </si>
+  <si>
+    <t>Pé de Serra</t>
+  </si>
+  <si>
+    <t>Pedrão</t>
+  </si>
+  <si>
+    <t>Pedro Alexandre</t>
+  </si>
+  <si>
+    <t>Piatã</t>
+  </si>
+  <si>
+    <t>Pilão Arcado</t>
+  </si>
+  <si>
+    <t>Pindaí</t>
+  </si>
+  <si>
+    <t>Pindobaçu</t>
+  </si>
+  <si>
+    <t>Pintadas</t>
+  </si>
+  <si>
+    <t>Piraí do Norte</t>
+  </si>
+  <si>
+    <t>Piripá</t>
+  </si>
+  <si>
+    <t>Piritiba</t>
+  </si>
+  <si>
+    <t>Planaltino</t>
+  </si>
+  <si>
+    <t>Planalto</t>
+  </si>
+  <si>
+    <t>Poções</t>
+  </si>
+  <si>
+    <t>Pojuca</t>
+  </si>
+  <si>
+    <t>Ponto Novo</t>
+  </si>
+  <si>
+    <t>Porto Seguro</t>
+  </si>
+  <si>
+    <t>Potiraguá</t>
+  </si>
+  <si>
+    <t>Prado</t>
+  </si>
+  <si>
+    <t>Presidente Dutra</t>
+  </si>
+  <si>
+    <t>Presidente Jânio Quadros</t>
+  </si>
+  <si>
+    <t>Presidente Tancredo Neves</t>
+  </si>
+  <si>
+    <t>Queimadas</t>
+  </si>
+  <si>
+    <t>Quijingue</t>
+  </si>
+  <si>
+    <t>Quixabeira</t>
+  </si>
+  <si>
+    <t>Rafael Jambeiro</t>
+  </si>
+  <si>
+    <t>Remanso</t>
+  </si>
+  <si>
+    <t>Retirolândia</t>
+  </si>
+  <si>
+    <t>Riachão das Neves</t>
+  </si>
+  <si>
+    <t>Riachão do Jacuípe</t>
+  </si>
+  <si>
+    <t>Riacho de Santana</t>
+  </si>
+  <si>
+    <t>Ribeira do Amparo</t>
+  </si>
+  <si>
+    <t>Ribeira do Pombal</t>
+  </si>
+  <si>
+    <t>Ribeirão do Largo</t>
+  </si>
+  <si>
+    <t>Rio de Contas</t>
+  </si>
+  <si>
+    <t>Rio do Antônio</t>
+  </si>
+  <si>
+    <t>Rio do Pires</t>
+  </si>
+  <si>
+    <t>Rio Real</t>
+  </si>
+  <si>
+    <t>Rodelas</t>
+  </si>
+  <si>
+    <t>Ruy Barbosa</t>
+  </si>
+  <si>
+    <t>Salinas da Margarida</t>
+  </si>
+  <si>
+    <t>Salvador</t>
+  </si>
+  <si>
+    <t>Santa Bárbara</t>
+  </si>
+  <si>
+    <t>Santa Brígida</t>
+  </si>
+  <si>
+    <t>Santa Cruz Cabrália</t>
+  </si>
+  <si>
+    <t>Santa Cruz da Vitória</t>
+  </si>
+  <si>
+    <t>Santa Inês</t>
+  </si>
+  <si>
+    <t>Santa Luzia</t>
+  </si>
+  <si>
+    <t>Santa Maria da Vitória</t>
+  </si>
+  <si>
+    <t>Santa Rita de Cássia</t>
+  </si>
+  <si>
+    <t>Santa Terezinha</t>
+  </si>
+  <si>
+    <t>Santaluz</t>
+  </si>
+  <si>
+    <t>Santana</t>
+  </si>
+  <si>
+    <t>Santanópolis</t>
+  </si>
+  <si>
+    <t>Santo Amaro</t>
+  </si>
+  <si>
+    <t>Santo Antônio de Jesus</t>
+  </si>
+  <si>
+    <t>Santo Estêvão</t>
+  </si>
+  <si>
+    <t>São Desidério</t>
+  </si>
+  <si>
+    <t>São Domingos</t>
+  </si>
+  <si>
+    <t>São Felipe</t>
+  </si>
+  <si>
+    <t>São Félix</t>
+  </si>
+  <si>
+    <t>São Félix do Coribe</t>
+  </si>
+  <si>
+    <t>São Francisco do Conde</t>
+  </si>
+  <si>
+    <t>São Gabriel</t>
+  </si>
+  <si>
+    <t>São Gonçalo dos Campos</t>
+  </si>
+  <si>
+    <t>São José da Vitória</t>
+  </si>
+  <si>
+    <t>São José do Jacuípe</t>
+  </si>
+  <si>
+    <t>São Miguel das Matas</t>
+  </si>
+  <si>
+    <t>São Sebastião do Passé</t>
+  </si>
+  <si>
+    <t>Sapeaçu</t>
+  </si>
+  <si>
+    <t>Sátiro Dias</t>
+  </si>
+  <si>
+    <t>Saubara</t>
+  </si>
+  <si>
+    <t>Saúde</t>
+  </si>
+  <si>
+    <t>Seabra</t>
+  </si>
+  <si>
+    <t>Sebastião Laranjeiras</t>
+  </si>
+  <si>
+    <t>Senhor do Bonfim</t>
+  </si>
+  <si>
+    <t>Sento Sé</t>
+  </si>
+  <si>
+    <t>Serra do Ramalho</t>
+  </si>
+  <si>
+    <t>Serra Dourada</t>
+  </si>
+  <si>
+    <t>Serra Preta</t>
+  </si>
+  <si>
+    <t>Serrinha</t>
+  </si>
+  <si>
+    <t>Serrolândia</t>
+  </si>
+  <si>
+    <t>Simões Filho</t>
+  </si>
+  <si>
+    <t>Sítio do Mato</t>
+  </si>
+  <si>
+    <t>Sítio do Quinto</t>
+  </si>
+  <si>
+    <t>Sobradinho</t>
+  </si>
+  <si>
+    <t>Souto Soares</t>
+  </si>
+  <si>
+    <t>Tabocas do Brejo Velho</t>
+  </si>
+  <si>
+    <t>Tanhaçu</t>
+  </si>
+  <si>
+    <t>Tanque Novo</t>
+  </si>
+  <si>
+    <t>Tanquinho</t>
+  </si>
+  <si>
+    <t>Taperoá</t>
+  </si>
+  <si>
+    <t>Tapiramutá</t>
+  </si>
+  <si>
+    <t>Teixeira de Freitas</t>
+  </si>
+  <si>
+    <t>Teodoro Sampaio</t>
+  </si>
+  <si>
+    <t>Teofilândia</t>
+  </si>
+  <si>
+    <t>Teolândia</t>
+  </si>
+  <si>
+    <t>Terra Nova</t>
+  </si>
+  <si>
+    <t>Tremedal</t>
+  </si>
+  <si>
+    <t>Tucano</t>
+  </si>
+  <si>
+    <t>Uauá</t>
+  </si>
+  <si>
+    <t>Ubaíra</t>
+  </si>
+  <si>
+    <t>Ubaitaba</t>
+  </si>
+  <si>
+    <t>Ubatã</t>
+  </si>
+  <si>
+    <t>Uibaí</t>
+  </si>
+  <si>
+    <t>Umburanas</t>
+  </si>
+  <si>
+    <t>Una</t>
+  </si>
+  <si>
+    <t>Urandi</t>
+  </si>
+  <si>
+    <t>Uruçuca</t>
+  </si>
+  <si>
+    <t>Utinga</t>
+  </si>
+  <si>
+    <t>Valença</t>
+  </si>
+  <si>
+    <t>Valente</t>
+  </si>
+  <si>
+    <t>Várzea da Roça</t>
+  </si>
+  <si>
+    <t>Várzea do Poço</t>
+  </si>
+  <si>
+    <t>Várzea Nova</t>
+  </si>
+  <si>
+    <t>Varzedo</t>
+  </si>
+  <si>
+    <t>Vera Cruz</t>
+  </si>
+  <si>
+    <t>Vereda</t>
+  </si>
+  <si>
+    <t>Vitória da Conquista</t>
+  </si>
+  <si>
+    <t>Wagner</t>
+  </si>
+  <si>
+    <t>Wanderley</t>
+  </si>
+  <si>
+    <t>Wenceslau Guimarães</t>
+  </si>
+  <si>
+    <t>Xique-Xique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILHÉUS </t>
   </si>
 </sst>
 </file>
@@ -2738,11 +3999,18 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$R$ -416]#,##0.00"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2907,6 +4175,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="13">
     <fill>
@@ -2982,7 +4263,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -3083,397 +4364,425 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="4" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="17" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="23" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="24" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="20" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3703,16 +5012,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="138" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C1" s="138" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D1" s="138" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="138" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -4985,13 +6294,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="149" t="s">
         <v>432</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="111" t="s">
@@ -12786,30 +14095,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="141" t="s">
         <v>533</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="143"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="142"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="144"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:26" ht="34.5" customHeight="1">
       <c r="A3" s="115"/>
@@ -13206,13 +14515,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="27.75">
-      <c r="A1" s="150" t="s">
+      <c r="A1" s="149" t="s">
         <v>543</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="111" t="s">
@@ -14230,8 +15539,8 @@
       <c r="A2" t="s">
         <v>40</v>
       </c>
-      <c r="B2" t="s">
-        <v>611</v>
+      <c r="B2" s="158" t="s">
+        <v>1309</v>
       </c>
       <c r="C2" t="s">
         <v>39</v>
@@ -14265,13 +15574,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C4" t="s">
         <v>21</v>
       </c>
       <c r="D4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -14282,7 +15591,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C5" t="s">
         <v>64</v>
@@ -14296,7 +15605,7 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B6" t="s">
         <v>476</v>
@@ -14333,7 +15642,7 @@
         <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C8" t="s">
         <v>46</v>
@@ -14368,6 +15677,3363 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75CA448A-85F8-4430-8C06-4AC58EC34D10}">
+  <dimension ref="A1:B418"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="24.75" customHeight="1" thickBot="1">
+      <c r="A1" s="154" t="s">
+        <v>889</v>
+      </c>
+      <c r="B1" s="155" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A2" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B2" s="157" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A3" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B3" s="157" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A4" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B4" s="157" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A5" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B5" s="157" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A6" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B6" s="157" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A7" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B7" s="157" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A8" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B8" s="157" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A9" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B9" s="157" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A10" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B10" s="157" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A11" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B11" s="157" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A12" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B12" s="157" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A13" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B13" s="157" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A14" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B14" s="157" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A15" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B15" s="157" t="s">
+        <v>905</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A16" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B16" s="157" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A17" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B17" s="157" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A18" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B18" s="157" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A19" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B19" s="157" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A20" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B20" s="157" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A21" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B21" s="157" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A22" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B22" s="157" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A23" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B23" s="157" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A24" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B24" s="157" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A25" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B25" s="157" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A26" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B26" s="157" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A27" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B27" s="157" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A28" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B28" s="157" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A29" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B29" s="157" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A30" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B30" s="157" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A31" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B31" s="157" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A32" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B32" s="157" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A33" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B33" s="157" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A34" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B34" s="157" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A35" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B35" s="157" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A36" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B36" s="157" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A37" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B37" s="157" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A38" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B38" s="157" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A39" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B39" s="157" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A40" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B40" s="157" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A41" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B41" s="157" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A42" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B42" s="157" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A43" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B43" s="157" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A44" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B44" s="157" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A45" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B45" s="157" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A46" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B46" s="157" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A47" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B47" s="157" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A48" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B48" s="157" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A49" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B49" s="157" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A50" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B50" s="157" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A51" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B51" s="157" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A52" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B52" s="157" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A53" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B53" s="157" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A54" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B54" s="157" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A55" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B55" s="157" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A56" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B56" s="157" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A57" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B57" s="157" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A58" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B58" s="157" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A59" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B59" s="157" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A60" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B60" s="157" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A61" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B61" s="157" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A62" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B62" s="157" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A63" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B63" s="157" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A64" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B64" s="157" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A65" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B65" s="157" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A66" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B66" s="157" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A67" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B67" s="157" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A68" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B68" s="157" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A69" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B69" s="157" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A70" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B70" s="157" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A71" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B71" s="157" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A72" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B72" s="157" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A73" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B73" s="157" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A74" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B74" s="157" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A75" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B75" s="157" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A76" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B76" s="157" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A77" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B77" s="157" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A78" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B78" s="157" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A79" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B79" s="157" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A80" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B80" s="157" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A81" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B81" s="157" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A82" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B82" s="157" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A83" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B83" s="157" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A84" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B84" s="157" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A85" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B85" s="157" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A86" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B86" s="157" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A87" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B87" s="157" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A88" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B88" s="157" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A89" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B89" s="157" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A90" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B90" s="157" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A91" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B91" s="157" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A92" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B92" s="157" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A93" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B93" s="157" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A94" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B94" s="157" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A95" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B95" s="157" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A96" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B96" s="157" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A97" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B97" s="157" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A98" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B98" s="157" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A99" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B99" s="157" t="s">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A100" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B100" s="157" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A101" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B101" s="157" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A102" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B102" s="157" t="s">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A103" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B103" s="157" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A104" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B104" s="157" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A105" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B105" s="157" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A106" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B106" s="157" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A107" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B107" s="157" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A108" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B108" s="157" t="s">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A109" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B109" s="157" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A110" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B110" s="157" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A111" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B111" s="157" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A112" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B112" s="157" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A113" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B113" s="157" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A114" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B114" s="157" t="s">
+        <v>1004</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A115" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B115" s="157" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A116" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B116" s="157" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A117" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B117" s="157" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A118" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B118" s="157" t="s">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A119" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B119" s="157" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A120" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B120" s="157" t="s">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A121" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B121" s="157" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A122" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B122" s="157" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A123" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B123" s="157" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A124" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B124" s="157" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A125" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B125" s="157" t="s">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A126" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B126" s="157" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A127" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B127" s="157" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A128" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B128" s="157" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A129" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B129" s="157" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A130" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B130" s="157" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A131" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B131" s="157" t="s">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A132" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B132" s="157" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A133" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B133" s="157" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A134" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B134" s="157" t="s">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A135" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B135" s="157" t="s">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A136" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B136" s="157" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A137" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B137" s="157" t="s">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="138" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A138" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B138" s="157" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="139" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A139" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B139" s="157" t="s">
+        <v>1029</v>
+      </c>
+    </row>
+    <row r="140" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A140" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B140" s="157" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="141" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A141" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B141" s="157" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="142" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A142" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B142" s="157" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="143" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A143" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B143" s="157" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="144" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A144" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B144" s="157" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A145" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B145" s="157" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="146" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A146" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B146" s="157" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="147" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A147" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B147" s="157" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="148" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A148" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B148" s="157" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="149" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A149" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B149" s="157" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="150" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A150" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B150" s="157" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="151" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A151" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B151" s="157" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A152" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B152" s="157" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A153" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B153" s="157" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A154" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B154" s="157" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="155" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A155" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B155" s="157" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="156" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A156" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B156" s="157" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="157" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A157" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B157" s="157" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="158" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A158" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B158" s="157" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="159" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A159" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B159" s="157" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="160" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A160" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B160" s="157" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="161" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A161" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B161" s="157" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="162" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A162" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B162" s="157" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="163" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A163" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B163" s="157" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="164" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A164" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B164" s="157" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="165" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A165" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B165" s="157" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="166" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A166" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B166" s="157" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="167" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A167" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B167" s="157" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="168" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A168" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B168" s="157" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="169" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A169" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B169" s="157" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="170" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A170" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B170" s="157" t="s">
+        <v>1060</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A171" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B171" s="157" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="172" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A172" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B172" s="157" t="s">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="173" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A173" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B173" s="157" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="174" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A174" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B174" s="157" t="s">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="175" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A175" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B175" s="157" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="176" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A176" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B176" s="157" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="177" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A177" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B177" s="157" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="178" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A178" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B178" s="157" t="s">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="179" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A179" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B179" s="157" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="180" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A180" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B180" s="157" t="s">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="181" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A181" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B181" s="157" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="182" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A182" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B182" s="157" t="s">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="183" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A183" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B183" s="157" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="184" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A184" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B184" s="157" t="s">
+        <v>1074</v>
+      </c>
+    </row>
+    <row r="185" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A185" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B185" s="157" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="186" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A186" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B186" s="157" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="187" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A187" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B187" s="157" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="188" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A188" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B188" s="157" t="s">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="189" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A189" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B189" s="157" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="190" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A190" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B190" s="157" t="s">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="191" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A191" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B191" s="157" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="192" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A192" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B192" s="157" t="s">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="193" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A193" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B193" s="157" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="194" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A194" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B194" s="157" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="195" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A195" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B195" s="157" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="196" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A196" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B196" s="157" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="197" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A197" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B197" s="157" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="198" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A198" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B198" s="157" t="s">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="199" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A199" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B199" s="157" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="200" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A200" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B200" s="157" t="s">
+        <v>1090</v>
+      </c>
+    </row>
+    <row r="201" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A201" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B201" s="157" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="202" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A202" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B202" s="157" t="s">
+        <v>1092</v>
+      </c>
+    </row>
+    <row r="203" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A203" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B203" s="157" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="204" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A204" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B204" s="157" t="s">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="205" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A205" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B205" s="157" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="206" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A206" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B206" s="157" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="207" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A207" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B207" s="157" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="208" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A208" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B208" s="157" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A209" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B209" s="157" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A210" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B210" s="157" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A211" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B211" s="157" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A212" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B212" s="157" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A213" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B213" s="157" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A214" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B214" s="157" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A215" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B215" s="157" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A216" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B216" s="157" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A217" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B217" s="157" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A218" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B218" s="157" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A219" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B219" s="157" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A220" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B220" s="157" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A221" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B221" s="157" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A222" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B222" s="157" t="s">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A223" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B223" s="157" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A224" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B224" s="157" t="s">
+        <v>1114</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A225" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B225" s="157" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A226" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B226" s="157" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A227" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B227" s="157" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A228" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B228" s="157" t="s">
+        <v>1118</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A229" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B229" s="157" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A230" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B230" s="157" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A231" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B231" s="157" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A232" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B232" s="157" t="s">
+        <v>1122</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A233" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B233" s="157" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A234" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B234" s="157" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" ht="32.25" thickBot="1">
+      <c r="A235" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B235" s="157" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A236" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B236" s="157" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A237" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B237" s="157" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A238" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B238" s="157" t="s">
+        <v>1128</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A239" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B239" s="157" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A240" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B240" s="157" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="241" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A241" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B241" s="157" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="242" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A242" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B242" s="157" t="s">
+        <v>1132</v>
+      </c>
+    </row>
+    <row r="243" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A243" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B243" s="157" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="244" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A244" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B244" s="157" t="s">
+        <v>1134</v>
+      </c>
+    </row>
+    <row r="245" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A245" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B245" s="157" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="246" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A246" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B246" s="157" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="247" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A247" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B247" s="157" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="248" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A248" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B248" s="157" t="s">
+        <v>1138</v>
+      </c>
+    </row>
+    <row r="249" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A249" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B249" s="157" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="250" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A250" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B250" s="157" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="251" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A251" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B251" s="157" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="252" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A252" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B252" s="157" t="s">
+        <v>1142</v>
+      </c>
+    </row>
+    <row r="253" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A253" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B253" s="157" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="254" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A254" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B254" s="157" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="255" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A255" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B255" s="157" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="256" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A256" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B256" s="157" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="257" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A257" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B257" s="157" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="258" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A258" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B258" s="157" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="259" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A259" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B259" s="157" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="260" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A260" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B260" s="157" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="261" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A261" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B261" s="157" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="262" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A262" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B262" s="157" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="263" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A263" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B263" s="157" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="264" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A264" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B264" s="157" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="265" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A265" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B265" s="157" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="266" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A266" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B266" s="157" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="267" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A267" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B267" s="157" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="268" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A268" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B268" s="157" t="s">
+        <v>1158</v>
+      </c>
+    </row>
+    <row r="269" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A269" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B269" s="157" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="270" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A270" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B270" s="157" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="271" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A271" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B271" s="157" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="272" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A272" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B272" s="157" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="273" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A273" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B273" s="157" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="274" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A274" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B274" s="157" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="275" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A275" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B275" s="157" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="276" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A276" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B276" s="157" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="277" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A277" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B277" s="157" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="278" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A278" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B278" s="157" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="279" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A279" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B279" s="157" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="280" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A280" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B280" s="157" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="281" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A281" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B281" s="157" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="282" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A282" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B282" s="157" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="283" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A283" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B283" s="157" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="284" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A284" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B284" s="157" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="285" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A285" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B285" s="157" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="286" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A286" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B286" s="157" t="s">
+        <v>1176</v>
+      </c>
+    </row>
+    <row r="287" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A287" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B287" s="157" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="288" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A288" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B288" s="157" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="289" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A289" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B289" s="157" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="290" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A290" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B290" s="157" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="291" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A291" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B291" s="157" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="292" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A292" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B292" s="157" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="293" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A293" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B293" s="157" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="294" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A294" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B294" s="157" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="295" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A295" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B295" s="157" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="296" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A296" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B296" s="157" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="297" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A297" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B297" s="157" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="298" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A298" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B298" s="157" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="299" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A299" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B299" s="157" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="300" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A300" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B300" s="157" t="s">
+        <v>1190</v>
+      </c>
+    </row>
+    <row r="301" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A301" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B301" s="157" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="302" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A302" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B302" s="157" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="303" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A303" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B303" s="157" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="304" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A304" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B304" s="157" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A305" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B305" s="157" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A306" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B306" s="157" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A307" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B307" s="157" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A308" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B308" s="157" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A309" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B309" s="157" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A310" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B310" s="157" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A311" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B311" s="157" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A312" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B312" s="157" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A313" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B313" s="157" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A314" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B314" s="157" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A315" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B315" s="157" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A316" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B316" s="157" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" ht="32.25" thickBot="1">
+      <c r="A317" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B317" s="157" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A318" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B318" s="157" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A319" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B319" s="157" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A320" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B320" s="157" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="321" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A321" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B321" s="157" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="322" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A322" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B322" s="157" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="323" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A323" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B323" s="157" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="324" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A324" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B324" s="157" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="325" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A325" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B325" s="157" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="326" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A326" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B326" s="157" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="327" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A327" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B327" s="157" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="328" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A328" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B328" s="157" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="329" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A329" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B329" s="157" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="330" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A330" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B330" s="157" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="331" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A331" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B331" s="157" t="s">
+        <v>1221</v>
+      </c>
+    </row>
+    <row r="332" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A332" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B332" s="157" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="333" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A333" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B333" s="157" t="s">
+        <v>1223</v>
+      </c>
+    </row>
+    <row r="334" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A334" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B334" s="157" t="s">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="335" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A335" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B335" s="157" t="s">
+        <v>1225</v>
+      </c>
+    </row>
+    <row r="336" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A336" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B336" s="157" t="s">
+        <v>1226</v>
+      </c>
+    </row>
+    <row r="337" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A337" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B337" s="157" t="s">
+        <v>1227</v>
+      </c>
+    </row>
+    <row r="338" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A338" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B338" s="157" t="s">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="339" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A339" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B339" s="157" t="s">
+        <v>1229</v>
+      </c>
+    </row>
+    <row r="340" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A340" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B340" s="157" t="s">
+        <v>1230</v>
+      </c>
+    </row>
+    <row r="341" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A341" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B341" s="157" t="s">
+        <v>1231</v>
+      </c>
+    </row>
+    <row r="342" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A342" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B342" s="157" t="s">
+        <v>1232</v>
+      </c>
+    </row>
+    <row r="343" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A343" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B343" s="157" t="s">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="344" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A344" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B344" s="157" t="s">
+        <v>1234</v>
+      </c>
+    </row>
+    <row r="345" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A345" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B345" s="157" t="s">
+        <v>1235</v>
+      </c>
+    </row>
+    <row r="346" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A346" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B346" s="157" t="s">
+        <v>1236</v>
+      </c>
+    </row>
+    <row r="347" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A347" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B347" s="157" t="s">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="348" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A348" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B348" s="157" t="s">
+        <v>1238</v>
+      </c>
+    </row>
+    <row r="349" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A349" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B349" s="157" t="s">
+        <v>1239</v>
+      </c>
+    </row>
+    <row r="350" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A350" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B350" s="157" t="s">
+        <v>1240</v>
+      </c>
+    </row>
+    <row r="351" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A351" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B351" s="157" t="s">
+        <v>1241</v>
+      </c>
+    </row>
+    <row r="352" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A352" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B352" s="157" t="s">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A353" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B353" s="157" t="s">
+        <v>1243</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A354" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B354" s="157" t="s">
+        <v>1244</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A355" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B355" s="157" t="s">
+        <v>1245</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A356" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B356" s="157" t="s">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A357" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B357" s="157" t="s">
+        <v>1247</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A358" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B358" s="157" t="s">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A359" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B359" s="157" t="s">
+        <v>1249</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A360" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B360" s="157" t="s">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A361" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B361" s="157" t="s">
+        <v>1251</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A362" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B362" s="157" t="s">
+        <v>1252</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A363" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B363" s="157" t="s">
+        <v>1253</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A364" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B364" s="157" t="s">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A365" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B365" s="157" t="s">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A366" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B366" s="157" t="s">
+        <v>1256</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A367" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B367" s="157" t="s">
+        <v>1257</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A368" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B368" s="157" t="s">
+        <v>1258</v>
+      </c>
+    </row>
+    <row r="369" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A369" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B369" s="157" t="s">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="370" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A370" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B370" s="157" t="s">
+        <v>1260</v>
+      </c>
+    </row>
+    <row r="371" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A371" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B371" s="157" t="s">
+        <v>1261</v>
+      </c>
+    </row>
+    <row r="372" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A372" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B372" s="157" t="s">
+        <v>1262</v>
+      </c>
+    </row>
+    <row r="373" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A373" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B373" s="157" t="s">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="374" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A374" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B374" s="157" t="s">
+        <v>1264</v>
+      </c>
+    </row>
+    <row r="375" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A375" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B375" s="157" t="s">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="376" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A376" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B376" s="157" t="s">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="377" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A377" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B377" s="157" t="s">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="378" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A378" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B378" s="157" t="s">
+        <v>1268</v>
+      </c>
+    </row>
+    <row r="379" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A379" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B379" s="157" t="s">
+        <v>1269</v>
+      </c>
+    </row>
+    <row r="380" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A380" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B380" s="157" t="s">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="381" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A381" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B381" s="157" t="s">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="382" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A382" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B382" s="157" t="s">
+        <v>1272</v>
+      </c>
+    </row>
+    <row r="383" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A383" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B383" s="157" t="s">
+        <v>1273</v>
+      </c>
+    </row>
+    <row r="384" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A384" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B384" s="157" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="385" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A385" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B385" s="157" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="386" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A386" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B386" s="157" t="s">
+        <v>1276</v>
+      </c>
+    </row>
+    <row r="387" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A387" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B387" s="157" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="388" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A388" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B388" s="157" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="389" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A389" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B389" s="157" t="s">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="390" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A390" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B390" s="157" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="391" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A391" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B391" s="157" t="s">
+        <v>1281</v>
+      </c>
+    </row>
+    <row r="392" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A392" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B392" s="157" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="393" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A393" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B393" s="157" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="394" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A394" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B394" s="157" t="s">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="395" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A395" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B395" s="157" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="396" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A396" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B396" s="157" t="s">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="397" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A397" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B397" s="157" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="398" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A398" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B398" s="157" t="s">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="399" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A399" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B399" s="157" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="400" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A400" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B400" s="157" t="s">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="401" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A401" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B401" s="157" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="402" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A402" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B402" s="157" t="s">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="403" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A403" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B403" s="157" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="404" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A404" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B404" s="157" t="s">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="405" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A405" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B405" s="157" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="406" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A406" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B406" s="157" t="s">
+        <v>1296</v>
+      </c>
+    </row>
+    <row r="407" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A407" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B407" s="157" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="408" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A408" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B408" s="157" t="s">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="409" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A409" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B409" s="157" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="410" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A410" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B410" s="157" t="s">
+        <v>1300</v>
+      </c>
+    </row>
+    <row r="411" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A411" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B411" s="157" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="412" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A412" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B412" s="157" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="413" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A413" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B413" s="157" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="414" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A414" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B414" s="157" t="s">
+        <v>1304</v>
+      </c>
+    </row>
+    <row r="415" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A415" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B415" s="157" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="416" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A416" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B416" s="157" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A417" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B417" s="157" t="s">
+        <v>1307</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" ht="16.5" thickBot="1">
+      <c r="A418" s="156" t="s">
+        <v>891</v>
+      </c>
+      <c r="B418" s="157" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -14384,33 +19050,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="151" t="s">
-        <v>708</v>
-      </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="141"/>
+      <c r="A1" s="150" t="s">
+        <v>707</v>
+      </c>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="29"/>
       <c r="L1" s="29"/>
       <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="142"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="144"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="146"/>
       <c r="K2" s="29"/>
       <c r="L2" s="29"/>
       <c r="M2" s="29"/>
@@ -14518,10 +19184,10 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="9" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>205</v>
@@ -14631,7 +19297,7 @@
         <v>15</v>
       </c>
       <c r="J8" s="105" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="K8" s="29"/>
       <c r="L8" s="29"/>
@@ -14678,7 +19344,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>239</v>
@@ -14703,7 +19369,7 @@
         <v>15</v>
       </c>
       <c r="J10" s="105" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="K10" s="29"/>
       <c r="L10" s="29"/>
@@ -14823,7 +19489,7 @@
         <v>15</v>
       </c>
       <c r="J13" s="9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="K13" s="29"/>
       <c r="L13" s="29"/>
@@ -14834,7 +19500,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
@@ -14855,7 +19521,7 @@
         <v>35</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K14" s="29"/>
       <c r="L14" s="29"/>
@@ -14887,7 +19553,7 @@
         <v>35</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="K15" s="29"/>
       <c r="L15" s="29"/>
@@ -14895,10 +19561,10 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" s="4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>587</v>
@@ -14947,13 +19613,13 @@
         <v>11</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>716</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>717</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>718</v>
-      </c>
       <c r="D17" s="5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E17" s="5">
         <v>3</v>
@@ -14972,7 +19638,7 @@
         <v>35</v>
       </c>
       <c r="J17" s="9" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="K17" s="29"/>
       <c r="L17" s="29"/>
@@ -15078,7 +19744,7 @@
     <row r="21" spans="1:26" ht="15" customHeight="1">
       <c r="A21" s="9"/>
       <c r="B21" s="9" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C21" s="9"/>
       <c r="D21" s="106" t="s">
@@ -15148,7 +19814,7 @@
     <row r="25" spans="1:26">
       <c r="A25" s="9"/>
       <c r="B25" s="9" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9"/>
@@ -20055,7 +24721,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -20069,13 +24735,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="150" t="s">
-        <v>722</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="A1" s="149" t="s">
+        <v>721</v>
+      </c>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="111" t="s">
@@ -20102,13 +24768,13 @@
         <v>360</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D3" s="12" t="s">
         <v>29</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -20125,15 +24791,15 @@
         <v>29</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="11" t="s">
+        <v>725</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>726</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>727</v>
       </c>
       <c r="C5" s="10" t="s">
         <v>102</v>
@@ -20142,7 +24808,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -20150,7 +24816,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C6" s="10" t="s">
         <v>13</v>
@@ -20159,7 +24825,7 @@
         <v>29</v>
       </c>
       <c r="E6" s="12" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -20176,15 +24842,15 @@
         <v>29</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="12" t="s">
+        <v>728</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>729</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>730</v>
       </c>
       <c r="C8" s="12" t="s">
         <v>64</v>
@@ -20193,7 +24859,7 @@
         <v>29</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -20201,7 +24867,7 @@
         <v>11</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C9" s="10" t="s">
         <v>402</v>
@@ -20210,7 +24876,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -20227,7 +24893,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -20244,7 +24910,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -20252,7 +24918,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>102</v>
@@ -20261,15 +24927,15 @@
         <v>29</v>
       </c>
       <c r="E12" s="12" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13" s="11" t="s">
+        <v>730</v>
+      </c>
+      <c r="B13" s="10" t="s">
         <v>731</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>732</v>
       </c>
       <c r="C13" s="10" t="s">
         <v>141</v>
@@ -20286,7 +24952,7 @@
         <v>80</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C14" s="11" t="s">
         <v>587</v>
@@ -20303,7 +24969,7 @@
         <v>80</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>31</v>
@@ -20312,7 +24978,7 @@
         <v>29</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -20320,7 +24986,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C16" s="10" t="s">
         <v>21</v>
@@ -20329,15 +24995,15 @@
         <v>29</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C17" s="10" t="s">
         <v>102</v>
@@ -20346,7 +25012,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -20354,7 +25020,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C18" s="10" t="s">
         <v>31</v>
@@ -20363,7 +25029,7 @@
         <v>29</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -20371,7 +25037,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C19" s="10" t="s">
         <v>64</v>
@@ -20380,7 +25046,7 @@
         <v>29</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -20397,7 +25063,7 @@
         <v>29</v>
       </c>
       <c r="E20" s="12" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -20414,7 +25080,7 @@
         <v>25</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -20422,7 +25088,7 @@
         <v>11</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C22" s="10" t="s">
         <v>13</v>
@@ -20431,7 +25097,7 @@
         <v>29</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -20439,7 +25105,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C23" s="10" t="s">
         <v>141</v>
@@ -20448,15 +25114,15 @@
         <v>29</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="10" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C24" s="10" t="s">
         <v>227</v>
@@ -20465,7 +25131,7 @@
         <v>29</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -20473,7 +25139,7 @@
         <v>11</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C25" s="10" t="s">
         <v>361</v>
@@ -20482,7 +25148,7 @@
         <v>29</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -20499,7 +25165,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -20507,16 +25173,16 @@
         <v>80</v>
       </c>
       <c r="B27" s="10" t="s">
+        <v>743</v>
+      </c>
+      <c r="C27" s="10" t="s">
         <v>744</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>745</v>
       </c>
       <c r="D27" s="10" t="s">
         <v>29</v>
       </c>
       <c r="E27" s="12" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -20533,7 +25199,7 @@
         <v>29</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -20541,7 +25207,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="10" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C29" s="10" t="s">
         <v>21</v>
@@ -20550,7 +25216,7 @@
         <v>29</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -20558,7 +25224,7 @@
         <v>23</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C30" s="10" t="s">
         <v>519</v>
@@ -20567,7 +25233,7 @@
         <v>25</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -20575,7 +25241,7 @@
         <v>11</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C31" s="10" t="s">
         <v>361</v>
@@ -20584,7 +25250,7 @@
         <v>29</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -20592,7 +25258,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="C32" s="10" t="s">
         <v>587</v>
@@ -20601,7 +25267,7 @@
         <v>29</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
     </row>
     <row r="33" spans="1:26">
@@ -20618,7 +25284,7 @@
         <v>25</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="34" spans="1:26">
@@ -20626,7 +25292,7 @@
         <v>23</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C34" s="10" t="s">
         <v>539</v>
@@ -20635,7 +25301,7 @@
         <v>25</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="35" spans="1:26">
@@ -20652,7 +25318,7 @@
         <v>25</v>
       </c>
       <c r="E35" s="12" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="36" spans="1:26">
@@ -20660,7 +25326,7 @@
         <v>23</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C36" s="10" t="s">
         <v>24</v>
@@ -20669,7 +25335,7 @@
         <v>25</v>
       </c>
       <c r="E36" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="37" spans="1:26">
@@ -20677,7 +25343,7 @@
         <v>80</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C37" s="10" t="s">
         <v>39</v>
@@ -20686,7 +25352,7 @@
         <v>25</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
     </row>
     <row r="38" spans="1:26">
@@ -20694,7 +25360,7 @@
         <v>23</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C38" s="10" t="s">
         <v>519</v>
@@ -20703,7 +25369,7 @@
         <v>25</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="39" spans="1:26">
@@ -20720,7 +25386,7 @@
         <v>25</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="40" spans="1:26">
@@ -20728,7 +25394,7 @@
         <v>11</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="C40" s="10" t="s">
         <v>21</v>
@@ -20737,7 +25403,7 @@
         <v>29</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
     </row>
     <row r="41" spans="1:26">
@@ -20745,16 +25411,16 @@
         <v>11</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>29</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="10"/>
@@ -20783,7 +25449,7 @@
         <v>23</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C42" s="10" t="s">
         <v>361</v>
@@ -20792,7 +25458,7 @@
         <v>25</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="43" spans="1:26">
@@ -20800,7 +25466,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C43" s="10" t="s">
         <v>46</v>
@@ -20809,7 +25475,7 @@
         <v>25</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="44" spans="1:26">
@@ -20826,7 +25492,7 @@
         <v>197</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="45" spans="1:26">
@@ -20843,7 +25509,7 @@
         <v>197</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="46" spans="1:26">
@@ -20851,7 +25517,7 @@
         <v>11</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="C46" s="10" t="s">
         <v>205</v>
@@ -20860,7 +25526,7 @@
         <v>25</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="47" spans="1:26">
@@ -20885,7 +25551,7 @@
         <v>32</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="C48" s="10" t="s">
         <v>64</v>
@@ -20894,7 +25560,7 @@
         <v>29</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="49" spans="1:26">
@@ -20902,7 +25568,7 @@
         <v>11</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C49" s="10" t="s">
         <v>141</v>
@@ -20911,7 +25577,7 @@
         <v>29</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
     </row>
     <row r="50" spans="1:26">
@@ -20919,7 +25585,7 @@
         <v>11</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C50" s="10" t="s">
         <v>361</v>
@@ -20928,15 +25594,15 @@
         <v>29</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
     </row>
     <row r="51" spans="1:26">
       <c r="A51" s="10" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C51" s="10" t="s">
         <v>590</v>
@@ -20945,7 +25611,7 @@
         <v>29</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="52" spans="1:26">
@@ -20953,7 +25619,7 @@
         <v>191</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C52" s="10" t="s">
         <v>21</v>
@@ -20979,7 +25645,7 @@
         <v>29</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
     </row>
     <row r="54" spans="1:26">
@@ -20987,7 +25653,7 @@
         <v>11</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C54" s="10" t="s">
         <v>37</v>
@@ -21004,7 +25670,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C55" s="10" t="s">
         <v>102</v>
@@ -21013,7 +25679,7 @@
         <v>29</v>
       </c>
       <c r="E55" s="12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="56" spans="1:26">
@@ -21021,7 +25687,7 @@
         <v>11</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C56" s="10" t="s">
         <v>21</v>
@@ -21030,7 +25696,7 @@
         <v>29</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="57" spans="1:26">
@@ -21038,7 +25704,7 @@
         <v>80</v>
       </c>
       <c r="B57" s="10" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C57" s="10" t="s">
         <v>102</v>
@@ -21047,7 +25713,7 @@
         <v>197</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="58" spans="1:26">
@@ -21055,7 +25721,7 @@
         <v>23</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C58" s="10" t="s">
         <v>162</v>
@@ -21064,7 +25730,7 @@
         <v>25</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="59" spans="1:26">
@@ -21081,7 +25747,7 @@
         <v>29</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="10"/>
@@ -21119,7 +25785,7 @@
         <v>25</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="61" spans="1:26">
@@ -21136,7 +25802,7 @@
         <v>29</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="62" spans="1:26">
@@ -21144,7 +25810,7 @@
         <v>32</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C62" s="10" t="s">
         <v>25</v>
@@ -21153,7 +25819,7 @@
         <v>539</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="63" spans="1:26">
@@ -21170,7 +25836,7 @@
         <v>29</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="64" spans="1:26">
@@ -21178,7 +25844,7 @@
         <v>11</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="C64" s="10" t="s">
         <v>64</v>
@@ -21187,7 +25853,7 @@
         <v>29</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -21204,7 +25870,7 @@
         <v>29</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -21212,7 +25878,7 @@
         <v>11</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="C66" s="10" t="s">
         <v>64</v>
@@ -21221,7 +25887,7 @@
         <v>29</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
     </row>
     <row r="67" spans="1:5">
@@ -21229,16 +25895,16 @@
         <v>11</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>29</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -21246,7 +25912,7 @@
         <v>80</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>102</v>
@@ -21255,7 +25921,7 @@
         <v>29</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -21263,7 +25929,7 @@
         <v>11</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="C69" s="10" t="s">
         <v>64</v>
@@ -21272,7 +25938,7 @@
         <v>29</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -21280,7 +25946,7 @@
         <v>23</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C70" s="10" t="s">
         <v>24</v>
@@ -21297,7 +25963,7 @@
         <v>23</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C71" s="10" t="s">
         <v>46</v>
@@ -21320,7 +25986,7 @@
         <v>29</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="73" spans="1:5">
@@ -21328,7 +25994,7 @@
         <v>80</v>
       </c>
       <c r="B73" s="10" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C73" s="10" t="s">
         <v>205</v>
@@ -21345,7 +26011,7 @@
         <v>23</v>
       </c>
       <c r="B74" s="125" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="C74" s="125" t="s">
         <v>39</v>
@@ -21354,7 +26020,7 @@
         <v>25</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="75" spans="1:5">
@@ -21371,7 +26037,7 @@
         <v>29</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
     </row>
     <row r="76" spans="1:5">
@@ -21388,7 +26054,7 @@
         <v>39</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -21396,7 +26062,7 @@
         <v>11</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C77" s="10" t="s">
         <v>34</v>
@@ -21422,7 +26088,7 @@
         <v>29</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
     </row>
     <row r="79" spans="1:5">
@@ -21439,7 +26105,7 @@
         <v>25</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
     </row>
     <row r="80" spans="1:5">
@@ -21456,7 +26122,7 @@
         <v>29</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="81" spans="1:5">
@@ -21473,7 +26139,7 @@
         <v>29</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
     </row>
     <row r="82" spans="1:5">
@@ -21490,7 +26156,7 @@
         <v>29</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
     </row>
     <row r="83" spans="1:5">
@@ -21498,16 +26164,16 @@
         <v>11</v>
       </c>
       <c r="B83" s="126" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C83" s="126" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D83" s="126" t="s">
         <v>29</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="84" spans="1:5">
@@ -21524,7 +26190,7 @@
         <v>25</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
     </row>
     <row r="85" spans="1:5">
@@ -21532,7 +26198,7 @@
         <v>23</v>
       </c>
       <c r="B85" s="114" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="C85" s="114" t="s">
         <v>21</v>
@@ -21541,7 +26207,7 @@
         <v>25</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -21549,7 +26215,7 @@
         <v>11</v>
       </c>
       <c r="B86" s="126" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C86" s="126" t="s">
         <v>51</v>
@@ -21558,7 +26224,7 @@
         <v>29</v>
       </c>
       <c r="E86" s="126" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -21569,7 +26235,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -21587,48 +26253,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="139" t="s">
-        <v>815</v>
-      </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="141"/>
+      <c r="A1" s="151" t="s">
+        <v>814</v>
+      </c>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="143"/>
       <c r="K1" s="29"/>
       <c r="L1" s="29"/>
       <c r="M1" s="29"/>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" s="152"/>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146"/>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146"/>
+      <c r="B2" s="140"/>
+      <c r="C2" s="140"/>
+      <c r="D2" s="140"/>
+      <c r="E2" s="140"/>
+      <c r="F2" s="140"/>
+      <c r="G2" s="140"/>
+      <c r="H2" s="140"/>
+      <c r="I2" s="140"/>
       <c r="J2" s="153"/>
       <c r="K2" s="29"/>
       <c r="L2" s="29"/>
       <c r="M2" s="29"/>
     </row>
     <row r="3" spans="1:26">
-      <c r="A3" s="142"/>
-      <c r="B3" s="143"/>
-      <c r="C3" s="143"/>
-      <c r="D3" s="143"/>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="143"/>
-      <c r="H3" s="143"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="144"/>
+      <c r="A3" s="144"/>
+      <c r="B3" s="145"/>
+      <c r="C3" s="145"/>
+      <c r="D3" s="145"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="145"/>
+      <c r="H3" s="145"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="146"/>
       <c r="K3" s="29"/>
       <c r="L3" s="29"/>
       <c r="M3" s="29"/>
@@ -21690,7 +26356,7 @@
         <v>396</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C6" s="18" t="s">
         <v>46</v>
@@ -21715,7 +26381,7 @@
         <v>35</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K6" s="97"/>
       <c r="L6" s="97"/>
@@ -21739,7 +26405,7 @@
         <v>396</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C7" s="18" t="s">
         <v>46</v>
@@ -21787,7 +26453,7 @@
         <v>11</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="C8" s="18" t="s">
         <v>31</v>
@@ -21861,7 +26527,7 @@
         <v>35</v>
       </c>
       <c r="J9" s="19" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="K9" s="49"/>
       <c r="L9" s="49"/>
@@ -21885,7 +26551,7 @@
         <v>23</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C10" s="18" t="s">
         <v>539</v>
@@ -21931,10 +26597,10 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" s="18" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="C11" s="18" t="s">
         <v>64</v>
@@ -22131,7 +26797,7 @@
     <row r="19" spans="1:13">
       <c r="A19" s="21"/>
       <c r="B19" s="21" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C19" s="21"/>
       <c r="D19" s="21"/>
@@ -28052,7 +32718,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
@@ -28066,13 +32732,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="150" t="s">
-        <v>821</v>
-      </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="A1" s="149" t="s">
+        <v>820</v>
+      </c>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="111" t="s">
@@ -28096,7 +32762,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="70" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C3" s="70" t="s">
         <v>34</v>
@@ -28105,7 +32771,7 @@
         <v>29</v>
       </c>
       <c r="E3" s="12" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -28122,7 +32788,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -28130,7 +32796,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="70" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="C5" s="70" t="s">
         <v>361</v>
@@ -28139,7 +32805,7 @@
         <v>29</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -28147,7 +32813,7 @@
         <v>80</v>
       </c>
       <c r="B6" s="70" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C6" s="70" t="s">
         <v>31</v>
@@ -28173,7 +32839,7 @@
         <v>29</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -28181,7 +32847,7 @@
         <v>80</v>
       </c>
       <c r="B8" s="70" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C8" s="70" t="s">
         <v>34</v>
@@ -28190,7 +32856,7 @@
         <v>29</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -28207,7 +32873,7 @@
         <v>29</v>
       </c>
       <c r="E9" s="12" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -28224,7 +32890,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="12" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -28232,7 +32898,7 @@
         <v>11</v>
       </c>
       <c r="B11" s="70" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C11" s="70" t="s">
         <v>51</v>
@@ -28241,7 +32907,7 @@
         <v>29</v>
       </c>
       <c r="E11" s="12" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -28249,7 +32915,7 @@
         <v>32</v>
       </c>
       <c r="B12" s="70" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C12" s="70" t="s">
         <v>361</v>
@@ -28258,7 +32924,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -28266,7 +32932,7 @@
         <v>80</v>
       </c>
       <c r="B13" s="70" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="C13" s="70" t="s">
         <v>361</v>
@@ -28275,7 +32941,7 @@
         <v>29</v>
       </c>
       <c r="E13" s="12" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -28292,7 +32958,7 @@
         <v>25</v>
       </c>
       <c r="E14" s="12" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -28309,7 +32975,7 @@
         <v>29</v>
       </c>
       <c r="E15" s="12" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -28317,7 +32983,7 @@
         <v>11</v>
       </c>
       <c r="B16" s="70" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C16" s="70" t="s">
         <v>107</v>
@@ -28326,7 +32992,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="12" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -28334,16 +33000,16 @@
         <v>11</v>
       </c>
       <c r="B17" s="70" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C17" s="70" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D17" s="70" t="s">
         <v>29</v>
       </c>
       <c r="E17" s="12" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -28351,7 +33017,7 @@
         <v>11</v>
       </c>
       <c r="B18" s="70" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C18" s="70" t="s">
         <v>64</v>
@@ -28360,7 +33026,7 @@
         <v>29</v>
       </c>
       <c r="E18" s="12" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -28377,7 +33043,7 @@
         <v>29</v>
       </c>
       <c r="E19" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -28411,7 +33077,7 @@
         <v>25</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -28428,7 +33094,7 @@
         <v>25</v>
       </c>
       <c r="E22" s="12" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -28436,7 +33102,7 @@
         <v>23</v>
       </c>
       <c r="B23" s="70" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C23" s="70" t="s">
         <v>46</v>
@@ -28445,7 +33111,7 @@
         <v>25</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -28462,7 +33128,7 @@
         <v>25</v>
       </c>
       <c r="E24" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -28479,7 +33145,7 @@
         <v>25</v>
       </c>
       <c r="E25" s="12" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -28496,7 +33162,7 @@
         <v>29</v>
       </c>
       <c r="E26" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -28504,7 +33170,7 @@
         <v>11</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>361</v>
@@ -28530,7 +33196,7 @@
         <v>29</v>
       </c>
       <c r="E28" s="12" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -28538,7 +33204,7 @@
         <v>80</v>
       </c>
       <c r="B29" s="70" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C29" s="70" t="s">
         <v>31</v>
@@ -28547,7 +33213,7 @@
         <v>29</v>
       </c>
       <c r="E29" s="12" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -28581,7 +33247,7 @@
         <v>29</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -28589,7 +33255,7 @@
         <v>11</v>
       </c>
       <c r="B32" s="70" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="C32" s="70" t="s">
         <v>361</v>
@@ -28598,7 +33264,7 @@
         <v>29</v>
       </c>
       <c r="E32" s="12" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="33" spans="1:26">
@@ -28606,7 +33272,7 @@
         <v>11</v>
       </c>
       <c r="B33" s="70" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C33" s="70" t="s">
         <v>361</v>
@@ -28615,7 +33281,7 @@
         <v>29</v>
       </c>
       <c r="E33" s="12" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
     </row>
     <row r="34" spans="1:26">
@@ -28623,7 +33289,7 @@
         <v>11</v>
       </c>
       <c r="B34" s="70" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C34" s="70" t="s">
         <v>51</v>
@@ -28632,7 +33298,7 @@
         <v>29</v>
       </c>
       <c r="E34" s="12" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="35" spans="1:26">
@@ -28640,7 +33306,7 @@
         <v>23</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C35" s="11" t="s">
         <v>361</v>
@@ -28649,7 +33315,7 @@
         <v>25</v>
       </c>
       <c r="E35" s="126" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="36" spans="1:26">
@@ -28666,7 +33332,7 @@
         <v>25</v>
       </c>
       <c r="E36" s="126" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="37" spans="1:26">
@@ -28683,7 +33349,7 @@
         <v>29</v>
       </c>
       <c r="E37" s="12" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="38" spans="1:26">
@@ -28691,7 +33357,7 @@
         <v>11</v>
       </c>
       <c r="B38" s="70" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="C38" s="70" t="s">
         <v>64</v>
@@ -28700,7 +33366,7 @@
         <v>29</v>
       </c>
       <c r="E38" s="12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
     </row>
     <row r="39" spans="1:26">
@@ -28717,7 +33383,7 @@
         <v>25</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
     </row>
     <row r="40" spans="1:26">
@@ -28725,7 +33391,7 @@
         <v>23</v>
       </c>
       <c r="B40" s="70" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="C40" s="70" t="s">
         <v>39</v>
@@ -28734,7 +33400,7 @@
         <v>25</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="10"/>
@@ -28763,7 +33429,7 @@
         <v>11</v>
       </c>
       <c r="B41" s="70" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C41" s="70" t="s">
         <v>21</v>
@@ -28772,7 +33438,7 @@
         <v>29</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="42" spans="1:26">
@@ -28780,7 +33446,7 @@
         <v>11</v>
       </c>
       <c r="B42" s="70" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="C42" s="70" t="s">
         <v>34</v>
@@ -28789,7 +33455,7 @@
         <v>29</v>
       </c>
       <c r="E42" s="12" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
     </row>
     <row r="43" spans="1:26">
@@ -28797,7 +33463,7 @@
         <v>11</v>
       </c>
       <c r="B43" s="70" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C43" s="70" t="s">
         <v>64</v>
@@ -28806,7 +33472,7 @@
         <v>29</v>
       </c>
       <c r="E43" s="12" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
     </row>
     <row r="44" spans="1:26">
@@ -28814,7 +33480,7 @@
         <v>80</v>
       </c>
       <c r="B44" s="70" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C44" s="70" t="s">
         <v>39</v>
@@ -28823,7 +33489,7 @@
         <v>25</v>
       </c>
       <c r="E44" s="12" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="45" spans="1:26">
@@ -28840,7 +33506,7 @@
         <v>29</v>
       </c>
       <c r="E45" s="12" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="46" spans="1:26">
@@ -28848,7 +33514,7 @@
         <v>11</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>456</v>
@@ -28857,7 +33523,7 @@
         <v>29</v>
       </c>
       <c r="E46" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="47" spans="1:26">
@@ -28874,7 +33540,7 @@
         <v>25</v>
       </c>
       <c r="E47" s="12" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
     </row>
     <row r="48" spans="1:26">
@@ -28891,7 +33557,7 @@
         <v>25</v>
       </c>
       <c r="E48" s="12" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="49" spans="1:26">
@@ -28908,7 +33574,7 @@
         <v>25</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="50" spans="1:26">
@@ -28916,16 +33582,16 @@
         <v>11</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D50" s="11" t="s">
         <v>29</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="51" spans="1:26">
@@ -28933,7 +33599,7 @@
         <v>32</v>
       </c>
       <c r="B51" s="11" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="C51" s="11" t="s">
         <v>64</v>
@@ -28942,7 +33608,7 @@
         <v>29</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
     </row>
     <row r="52" spans="1:26">
@@ -28959,7 +33625,7 @@
         <v>29</v>
       </c>
       <c r="E52" s="12" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="53" spans="1:26">
@@ -28967,7 +33633,7 @@
         <v>80</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>587</v>
@@ -28976,7 +33642,7 @@
         <v>29</v>
       </c>
       <c r="E53" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="54" spans="1:26">
@@ -28993,7 +33659,7 @@
         <v>25</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="55" spans="1:26">
@@ -29001,7 +33667,7 @@
         <v>11</v>
       </c>
       <c r="B55" s="70" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C55" s="70" t="s">
         <v>21</v>
@@ -29010,7 +33676,7 @@
         <v>29</v>
       </c>
       <c r="E55" s="126" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="56" spans="1:26">
@@ -29018,7 +33684,7 @@
         <v>23</v>
       </c>
       <c r="B56" s="70" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C56" s="70" t="s">
         <v>39</v>
@@ -29027,7 +33693,7 @@
         <v>25</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="57" spans="1:26">
@@ -29205,16 +33871,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="138" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="C1" s="138" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D1" s="138" t="s">
         <v>4</v>
       </c>
       <c r="E1" s="138" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="2" spans="1:5">
@@ -29231,7 +33897,7 @@
         <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -29248,7 +33914,7 @@
         <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -29265,7 +33931,7 @@
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -29273,7 +33939,7 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C5" t="s">
         <v>102</v>
@@ -29282,7 +33948,7 @@
         <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -29290,7 +33956,7 @@
         <v>23</v>
       </c>
       <c r="B6" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C6" t="s">
         <v>51</v>
@@ -29307,7 +33973,7 @@
         <v>23</v>
       </c>
       <c r="B7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C7" t="s">
         <v>24</v>
@@ -29333,7 +33999,7 @@
         <v>25</v>
       </c>
       <c r="E8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -29350,7 +34016,7 @@
         <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -29367,7 +34033,7 @@
         <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -29375,7 +34041,7 @@
         <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C11" t="s">
         <v>31</v>
@@ -29384,12 +34050,12 @@
         <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B12" t="s">
         <v>189</v>
@@ -29401,7 +34067,7 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -29409,7 +34075,7 @@
         <v>44</v>
       </c>
       <c r="B13" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C13" t="s">
         <v>31</v>
@@ -29418,7 +34084,7 @@
         <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -29452,7 +34118,7 @@
         <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -29469,7 +34135,7 @@
         <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -29486,7 +34152,7 @@
         <v>25</v>
       </c>
       <c r="E17" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -29494,7 +34160,7 @@
         <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C18" t="s">
         <v>31</v>
@@ -29503,7 +34169,7 @@
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -29511,7 +34177,7 @@
         <v>23</v>
       </c>
       <c r="B19" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C19" t="s">
         <v>205</v>
@@ -29537,7 +34203,7 @@
         <v>25</v>
       </c>
       <c r="E20" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -29562,7 +34228,7 @@
         <v>11</v>
       </c>
       <c r="B22" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C22" t="s">
         <v>292</v>
@@ -29571,15 +34237,15 @@
         <v>29</v>
       </c>
       <c r="E22" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B23" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C23" t="s">
         <v>107</v>
@@ -29588,7 +34254,7 @@
         <v>29</v>
       </c>
       <c r="E23" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -29596,7 +34262,7 @@
         <v>11</v>
       </c>
       <c r="B24" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C24" t="s">
         <v>13</v>
@@ -29605,7 +34271,7 @@
         <v>29</v>
       </c>
       <c r="E24" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -29622,7 +34288,7 @@
         <v>29</v>
       </c>
       <c r="E25" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -29639,7 +34305,7 @@
         <v>29</v>
       </c>
       <c r="E26" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -29647,7 +34313,7 @@
         <v>11</v>
       </c>
       <c r="B27" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C27" t="s">
         <v>102</v>
@@ -29656,7 +34322,7 @@
         <v>29</v>
       </c>
       <c r="E27" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -29664,7 +34330,7 @@
         <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C28" t="s">
         <v>361</v>
@@ -29673,7 +34339,7 @@
         <v>29</v>
       </c>
       <c r="E28" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -29681,7 +34347,7 @@
         <v>503</v>
       </c>
       <c r="B29" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C29" t="s">
         <v>402</v>
@@ -29690,7 +34356,7 @@
         <v>29</v>
       </c>
       <c r="E29" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -29707,7 +34373,7 @@
         <v>29</v>
       </c>
       <c r="E30" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -29715,7 +34381,7 @@
         <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C31" t="s">
         <v>587</v>
@@ -29724,7 +34390,7 @@
         <v>29</v>
       </c>
       <c r="E31" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -29741,7 +34407,7 @@
         <v>25</v>
       </c>
       <c r="E32" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -29749,7 +34415,7 @@
         <v>11</v>
       </c>
       <c r="B33" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C33" t="s">
         <v>46</v>
@@ -29758,7 +34424,7 @@
         <v>29</v>
       </c>
       <c r="E33" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -29775,7 +34441,7 @@
         <v>25</v>
       </c>
       <c r="E34" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -29792,7 +34458,7 @@
         <v>29</v>
       </c>
       <c r="E35" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -29809,7 +34475,7 @@
         <v>29</v>
       </c>
       <c r="E36" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -29817,7 +34483,7 @@
         <v>11</v>
       </c>
       <c r="B37" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C37" t="s">
         <v>51</v>
@@ -29826,7 +34492,7 @@
         <v>29</v>
       </c>
       <c r="E37" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -29834,7 +34500,7 @@
         <v>11</v>
       </c>
       <c r="B38" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C38" t="s">
         <v>102</v>
@@ -29843,7 +34509,7 @@
         <v>29</v>
       </c>
       <c r="E38" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -29851,7 +34517,7 @@
         <v>80</v>
       </c>
       <c r="B39" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C39" t="s">
         <v>587</v>
@@ -29860,15 +34526,15 @@
         <v>29</v>
       </c>
       <c r="E39" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B40" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C40" t="s">
         <v>21</v>
@@ -29877,7 +34543,7 @@
         <v>29</v>
       </c>
       <c r="E40" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -29885,7 +34551,7 @@
         <v>11</v>
       </c>
       <c r="B41" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C41" t="s">
         <v>51</v>
@@ -29894,7 +34560,7 @@
         <v>29</v>
       </c>
       <c r="E41" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -29902,7 +34568,7 @@
         <v>11</v>
       </c>
       <c r="B42" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C42" t="s">
         <v>102</v>
@@ -29911,7 +34577,7 @@
         <v>29</v>
       </c>
       <c r="E42" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -29919,7 +34585,7 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C43" t="s">
         <v>46</v>
@@ -29928,7 +34594,7 @@
         <v>29</v>
       </c>
       <c r="E43" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -29936,7 +34602,7 @@
         <v>11</v>
       </c>
       <c r="B44" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C44" t="s">
         <v>31</v>
@@ -29945,7 +34611,7 @@
         <v>29</v>
       </c>
       <c r="E44" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -29953,7 +34619,7 @@
         <v>11</v>
       </c>
       <c r="B45" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C45" t="s">
         <v>141</v>
@@ -29962,7 +34628,7 @@
         <v>29</v>
       </c>
       <c r="E45" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -29979,7 +34645,7 @@
         <v>29</v>
       </c>
       <c r="E46" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
     </row>
     <row r="47" spans="1:5">
@@ -29996,7 +34662,7 @@
         <v>29</v>
       </c>
       <c r="E47" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="48" spans="1:5">
@@ -30007,13 +34673,13 @@
         <v>91</v>
       </c>
       <c r="C48" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D48" t="s">
         <v>29</v>
       </c>
       <c r="E48" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
     </row>
     <row r="49" spans="1:5">
@@ -30030,15 +34696,15 @@
         <v>29</v>
       </c>
       <c r="E49" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
     </row>
     <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B50" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="C50" t="s">
         <v>102</v>
@@ -30047,7 +34713,7 @@
         <v>29</v>
       </c>
       <c r="E50" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -30055,7 +34721,7 @@
         <v>11</v>
       </c>
       <c r="B51" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C51" t="s">
         <v>239</v>
@@ -30064,12 +34730,12 @@
         <v>29</v>
       </c>
       <c r="E51" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
     </row>
     <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B52" t="s">
         <v>591</v>
@@ -30081,7 +34747,7 @@
         <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="53" spans="1:5">
@@ -30089,7 +34755,7 @@
         <v>11</v>
       </c>
       <c r="B53" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C53" t="s">
         <v>196</v>
@@ -30098,7 +34764,7 @@
         <v>29</v>
       </c>
       <c r="E53" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -30123,7 +34789,7 @@
         <v>11</v>
       </c>
       <c r="B55" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C55" t="s">
         <v>21</v>
@@ -30132,7 +34798,7 @@
         <v>29</v>
       </c>
       <c r="E55" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
     </row>
     <row r="56" spans="1:5">
@@ -30140,7 +34806,7 @@
         <v>32</v>
       </c>
       <c r="B56" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C56" t="s">
         <v>402</v>
@@ -30149,7 +34815,7 @@
         <v>29</v>
       </c>
       <c r="E56" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -30188,10 +34854,10 @@
     </row>
     <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B59" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C59" t="s">
         <v>34</v>
@@ -30200,7 +34866,7 @@
         <v>29</v>
       </c>
       <c r="E59" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="60" spans="1:5">
@@ -30217,7 +34883,7 @@
         <v>29</v>
       </c>
       <c r="E60" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="61" spans="1:5">
@@ -30251,7 +34917,7 @@
         <v>25</v>
       </c>
       <c r="E62" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
     </row>
     <row r="63" spans="1:5">
@@ -30268,7 +34934,7 @@
         <v>25</v>
       </c>
       <c r="E63" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
     </row>
     <row r="64" spans="1:5">
@@ -30285,7 +34951,7 @@
         <v>25</v>
       </c>
       <c r="E64" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
     </row>
     <row r="65" spans="1:5">
@@ -30293,7 +34959,7 @@
         <v>23</v>
       </c>
       <c r="B65" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C65" t="s">
         <v>205</v>
@@ -30310,7 +34976,7 @@
         <v>23</v>
       </c>
       <c r="B66" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C66" t="s">
         <v>505</v>
@@ -30327,7 +34993,7 @@
         <v>23</v>
       </c>
       <c r="B67" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="C67" t="s">
         <v>539</v>
@@ -30336,7 +35002,7 @@
         <v>25</v>
       </c>
       <c r="E67" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
     </row>
     <row r="68" spans="1:5">
@@ -30344,7 +35010,7 @@
         <v>11</v>
       </c>
       <c r="B68" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C68" t="s">
         <v>361</v>
@@ -30353,7 +35019,7 @@
         <v>29</v>
       </c>
       <c r="E68" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
     </row>
     <row r="69" spans="1:5">
@@ -30370,7 +35036,7 @@
         <v>25</v>
       </c>
       <c r="E69" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -30429,7 +35095,7 @@
         <v>11</v>
       </c>
       <c r="B73" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C73" t="s">
         <v>587</v>
@@ -30446,10 +35112,10 @@
         <v>11</v>
       </c>
       <c r="B74" t="s">
+        <v>704</v>
+      </c>
+      <c r="C74" t="s">
         <v>705</v>
-      </c>
-      <c r="C74" t="s">
-        <v>706</v>
       </c>
       <c r="D74" t="s">
         <v>29</v>
@@ -30463,7 +35129,7 @@
         <v>23</v>
       </c>
       <c r="B75" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C75" t="s">
         <v>46</v>
@@ -30472,7 +35138,7 @@
         <v>25</v>
       </c>
       <c r="E75" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -30784,13 +35450,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="15" customHeight="1">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="139" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:27">
       <c r="A2" s="13" t="s">
@@ -31832,30 +36498,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="147" t="s">
+      <c r="A1" s="141" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="143"/>
     </row>
     <row r="2" spans="1:26">
-      <c r="A2" s="142"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="144"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:26" ht="23.25">
       <c r="A3" s="31"/>
@@ -36168,13 +40834,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="139" t="s">
         <v>273</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13" t="s">
@@ -36980,30 +41646,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="148" t="s">
+      <c r="A1" s="147" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="143"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="142"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="144"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="A3" s="73"/>
@@ -40269,13 +44935,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="15" customHeight="1">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="139" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="146"/>
-      <c r="C1" s="146"/>
-      <c r="D1" s="146"/>
-      <c r="E1" s="146"/>
+      <c r="B1" s="140"/>
+      <c r="C1" s="140"/>
+      <c r="D1" s="140"/>
+      <c r="E1" s="140"/>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13" t="s">
@@ -41182,30 +45848,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="148" t="s">
         <v>416</v>
       </c>
-      <c r="B1" s="140"/>
-      <c r="C1" s="140"/>
-      <c r="D1" s="140"/>
-      <c r="E1" s="140"/>
-      <c r="F1" s="140"/>
-      <c r="G1" s="140"/>
-      <c r="H1" s="140"/>
-      <c r="I1" s="140"/>
-      <c r="J1" s="141"/>
+      <c r="B1" s="142"/>
+      <c r="C1" s="142"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="142"/>
+      <c r="F1" s="142"/>
+      <c r="G1" s="142"/>
+      <c r="H1" s="142"/>
+      <c r="I1" s="142"/>
+      <c r="J1" s="143"/>
     </row>
     <row r="2" spans="1:26" ht="23.25" customHeight="1">
-      <c r="A2" s="142"/>
-      <c r="B2" s="143"/>
-      <c r="C2" s="143"/>
-      <c r="D2" s="143"/>
-      <c r="E2" s="143"/>
-      <c r="F2" s="143"/>
-      <c r="G2" s="143"/>
-      <c r="H2" s="143"/>
-      <c r="I2" s="143"/>
-      <c r="J2" s="144"/>
+      <c r="A2" s="144"/>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
+      <c r="G2" s="145"/>
+      <c r="H2" s="145"/>
+      <c r="I2" s="145"/>
+      <c r="J2" s="146"/>
     </row>
     <row r="3" spans="1:26" ht="23.25" customHeight="1">
       <c r="A3" s="100"/>
